--- a/Resources/Sheet/DANTEST.xlsx
+++ b/Resources/Sheet/DANTEST.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hadz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5F4E2B-2CE2-4F57-98A9-C92D5187D6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDC4CD3-84D2-44EF-8FC1-29C8029DF474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="579" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" tabRatio="579" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QSTBKT" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="119">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -285,6 +285,120 @@
   </si>
   <si>
     <t>LL còn lại</t>
+  </si>
+  <si>
+    <t>LỰC LƯỢNG</t>
+  </si>
+  <si>
+    <t>1. Trong biên chế</t>
+  </si>
+  <si>
+    <t>dBB</t>
+  </si>
+  <si>
+    <t>2. LL phối thuộc</t>
+  </si>
+  <si>
+    <t>1 cO100/e</t>
+  </si>
+  <si>
+    <t>1 cSPG-9/e</t>
+  </si>
+  <si>
+    <t>1 cSMPK 12,7mm/e</t>
+  </si>
+  <si>
+    <t>1b VTB/e</t>
+  </si>
+  <si>
+    <t>1 tổ QY/e</t>
+  </si>
+  <si>
+    <t>1 bHH/f</t>
+  </si>
+  <si>
+    <t>1 c CB(-)/e</t>
+  </si>
+  <si>
+    <t>1 tổ SC/e</t>
+  </si>
+  <si>
+    <t>cBB7/dBB2</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t>cBB1</t>
+  </si>
+  <si>
+    <t>2. LL tăng cường</t>
+  </si>
+  <si>
+    <t>1 b SPG-9/e</t>
+  </si>
+  <si>
+    <t>cCo82(-)/d</t>
+  </si>
+  <si>
+    <t>b SMPK 12,7mm/e</t>
+  </si>
+  <si>
+    <t>cBB2 (-)</t>
+  </si>
+  <si>
+    <t>Y tá/d</t>
+  </si>
+  <si>
+    <t>Nuôi quân/d</t>
+  </si>
+  <si>
+    <t>a VTB</t>
+  </si>
+  <si>
+    <t>cBB7</t>
+  </si>
+  <si>
+    <t>1bSPG9/d</t>
+  </si>
+  <si>
+    <t>1bCo82/d</t>
+  </si>
+  <si>
+    <t>1bSMPK12,7</t>
+  </si>
+  <si>
+    <t>Nuôi quân</t>
+  </si>
+  <si>
+    <t>cBB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuôi quân </t>
+  </si>
+  <si>
+    <t>Lực lượng còn lại</t>
+  </si>
+  <si>
+    <t>2. Lực lượng tăng cường</t>
+  </si>
+  <si>
+    <t>1cCo100mm/e</t>
+  </si>
+  <si>
+    <t>1cSPG-9/e</t>
+  </si>
+  <si>
+    <t>1cSMPK12,7mm/e</t>
+  </si>
+  <si>
+    <t>1cCB(-)/e</t>
+  </si>
+  <si>
+    <t>1bHH/f</t>
+  </si>
+  <si>
+    <t>1bVTB/e</t>
   </si>
 </sst>
 </file>
@@ -1057,14 +1171,14 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="22" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1425,7 +1539,9 @@
       <c r="O2" s="166"/>
     </row>
     <row r="3" spans="1:32">
-      <c r="A3" s="167"/>
+      <c r="A3" s="167" t="s">
+        <v>81</v>
+      </c>
       <c r="B3" s="167"/>
       <c r="C3" s="167"/>
       <c r="D3" s="167"/>
@@ -1476,7 +1592,9 @@
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:32">
-      <c r="A6" s="5"/>
+      <c r="A6" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1493,7 +1611,9 @@
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:32" ht="18.899999999999999" customHeight="1">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -1510,7 +1630,9 @@
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:32">
-      <c r="A8" s="5"/>
+      <c r="A8" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1527,7 +1649,9 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:32">
-      <c r="A9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1544,7 +1668,9 @@
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:32">
-      <c r="A10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1561,7 +1687,9 @@
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:32">
-      <c r="A11" s="8"/>
+      <c r="A11" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1578,7 +1706,9 @@
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:32">
-      <c r="A12" s="8"/>
+      <c r="A12" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1595,7 +1725,9 @@
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:32">
-      <c r="A13" s="9"/>
+      <c r="A13" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -1612,7 +1744,9 @@
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:32">
-      <c r="A14" s="9"/>
+      <c r="A14" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -1629,7 +1763,9 @@
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:32">
-      <c r="A15" s="8"/>
+      <c r="A15" s="8" t="s">
+        <v>91</v>
+      </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1646,7 +1782,9 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:32">
-      <c r="A16" s="8"/>
+      <c r="A16" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -1679,7 +1817,9 @@
       <c r="AF16" s="12"/>
     </row>
     <row r="17" spans="1:32">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13" t="s">
+        <v>93</v>
+      </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -1745,7 +1885,9 @@
       <c r="AF18" s="12"/>
     </row>
     <row r="19" spans="1:32">
-      <c r="A19" s="20"/>
+      <c r="A19" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
@@ -1844,7 +1986,9 @@
       <c r="AF21" s="16"/>
     </row>
     <row r="22" spans="1:32">
-      <c r="A22" s="167"/>
+      <c r="A22" s="167" t="s">
+        <v>81</v>
+      </c>
       <c r="B22" s="167"/>
       <c r="C22" s="167"/>
       <c r="D22" s="167"/>
@@ -1911,7 +2055,9 @@
       <c r="O24" s="4"/>
     </row>
     <row r="25" spans="1:32">
-      <c r="A25" s="5"/>
+      <c r="A25" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -1928,7 +2074,9 @@
       <c r="O25" s="5"/>
     </row>
     <row r="26" spans="1:32">
-      <c r="A26" s="6"/>
+      <c r="A26" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -1945,7 +2093,9 @@
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:32">
-      <c r="A27" s="5"/>
+      <c r="A27" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -1962,7 +2112,9 @@
       <c r="O27" s="5"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="8"/>
+      <c r="A28" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -1979,7 +2131,9 @@
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="8"/>
+      <c r="A29" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1996,7 +2150,9 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:32">
-      <c r="A30" s="8"/>
+      <c r="A30" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -2013,7 +2169,9 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="8"/>
+      <c r="A31" s="8" t="s">
+        <v>100</v>
+      </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -2030,7 +2188,9 @@
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:32">
-      <c r="A32" s="9"/>
+      <c r="A32" s="9" t="s">
+        <v>101</v>
+      </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -2047,7 +2207,9 @@
       <c r="O32" s="4"/>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="9"/>
+      <c r="A33" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -2064,7 +2226,9 @@
       <c r="O33" s="4"/>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="8"/>
+      <c r="A34" s="8" t="s">
+        <v>103</v>
+      </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -2081,7 +2245,9 @@
       <c r="O34" s="4"/>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="20"/>
+      <c r="A36" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
@@ -2132,7 +2298,9 @@
       <c r="O38" s="166"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="167"/>
+      <c r="A39" s="167" t="s">
+        <v>81</v>
+      </c>
       <c r="B39" s="167"/>
       <c r="C39" s="167"/>
       <c r="D39" s="167"/>
@@ -2183,7 +2351,9 @@
       <c r="O41" s="4"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="5"/>
+      <c r="A42" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -2200,7 +2370,9 @@
       <c r="O42" s="5"/>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43" s="6"/>
+      <c r="A43" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -2217,7 +2389,9 @@
       <c r="O43" s="4"/>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="5"/>
+      <c r="A44" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -2234,7 +2408,9 @@
       <c r="O44" s="5"/>
     </row>
     <row r="45" spans="1:15">
-      <c r="A45" s="8"/>
+      <c r="A45" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -2251,7 +2427,9 @@
       <c r="O45" s="4"/>
     </row>
     <row r="46" spans="1:15">
-      <c r="A46" s="8"/>
+      <c r="A46" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -2268,7 +2446,9 @@
       <c r="O46" s="4"/>
     </row>
     <row r="47" spans="1:15">
-      <c r="A47" s="8"/>
+      <c r="A47" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -2285,7 +2465,9 @@
       <c r="O47" s="4"/>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" s="8"/>
+      <c r="A48" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -2336,7 +2518,9 @@
       <c r="O50" s="24"/>
     </row>
     <row r="51" spans="1:15">
-      <c r="A51" s="20"/>
+      <c r="A51" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
@@ -2387,7 +2571,9 @@
       <c r="O53" s="166"/>
     </row>
     <row r="54" spans="1:15">
-      <c r="A54" s="167"/>
+      <c r="A54" s="167" t="s">
+        <v>81</v>
+      </c>
       <c r="B54" s="167"/>
       <c r="C54" s="167"/>
       <c r="D54" s="167"/>
@@ -2438,7 +2624,9 @@
       <c r="O56" s="4"/>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" s="5"/>
+      <c r="A57" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -2455,7 +2643,9 @@
       <c r="O57" s="5"/>
     </row>
     <row r="58" spans="1:15">
-      <c r="A58" s="6"/>
+      <c r="A58" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -2472,7 +2662,9 @@
       <c r="O58" s="4"/>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" s="5"/>
+      <c r="A59" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -2489,7 +2681,9 @@
       <c r="O59" s="5"/>
     </row>
     <row r="60" spans="1:15" ht="18.45" customHeight="1">
-      <c r="A60" s="8"/>
+      <c r="A60" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -2523,7 +2717,9 @@
       <c r="O61" s="4"/>
     </row>
     <row r="62" spans="1:15">
-      <c r="A62" s="20"/>
+      <c r="A62" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
@@ -2574,7 +2770,9 @@
       <c r="O64" s="166"/>
     </row>
     <row r="65" spans="1:15">
-      <c r="A65" s="167"/>
+      <c r="A65" s="167" t="s">
+        <v>81</v>
+      </c>
       <c r="B65" s="167"/>
       <c r="C65" s="167"/>
       <c r="D65" s="167"/>
@@ -2625,7 +2823,9 @@
       <c r="O67" s="4"/>
     </row>
     <row r="68" spans="1:15">
-      <c r="A68" s="5"/>
+      <c r="A68" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -2642,7 +2842,9 @@
       <c r="O68" s="5"/>
     </row>
     <row r="69" spans="1:15">
-      <c r="A69" s="25"/>
+      <c r="A69" s="25" t="s">
+        <v>111</v>
+      </c>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
@@ -2657,8 +2859,10 @@
       <c r="N69" s="25"/>
       <c r="O69" s="25"/>
     </row>
-    <row r="70" spans="1:15">
-      <c r="A70" s="5"/>
+    <row r="70" spans="1:15" ht="34.799999999999997">
+      <c r="A70" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -2675,7 +2879,9 @@
       <c r="O70" s="5"/>
     </row>
     <row r="71" spans="1:15">
-      <c r="A71" s="8"/>
+      <c r="A71" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -2691,7 +2897,9 @@
       <c r="O71" s="4"/>
     </row>
     <row r="72" spans="1:15">
-      <c r="A72" s="8"/>
+      <c r="A72" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -2707,7 +2915,9 @@
       <c r="O72" s="4"/>
     </row>
     <row r="73" spans="1:15">
-      <c r="A73" s="8"/>
+      <c r="A73" s="8" t="s">
+        <v>115</v>
+      </c>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -2723,7 +2933,9 @@
       <c r="O73" s="4"/>
     </row>
     <row r="74" spans="1:15">
-      <c r="A74" s="8"/>
+      <c r="A74" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -2739,7 +2951,9 @@
       <c r="O74" s="4"/>
     </row>
     <row r="75" spans="1:15">
-      <c r="A75" s="9"/>
+      <c r="A75" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
@@ -2755,7 +2969,9 @@
       <c r="O75" s="4"/>
     </row>
     <row r="76" spans="1:15">
-      <c r="A76" s="9"/>
+      <c r="A76" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -2771,7 +2987,9 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" spans="1:15">
-      <c r="A77" s="9"/>
+      <c r="A77" s="9" t="s">
+        <v>118</v>
+      </c>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -2787,7 +3005,9 @@
       <c r="O77" s="4"/>
     </row>
     <row r="78" spans="1:15">
-      <c r="A78" s="8"/>
+      <c r="A78" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -2837,7 +3057,9 @@
       <c r="O80" s="4"/>
     </row>
     <row r="81" spans="1:15">
-      <c r="A81" s="20"/>
+      <c r="A81" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="B81" s="21"/>
       <c r="C81" s="21"/>
       <c r="D81" s="21"/>
@@ -4899,43 +5121,43 @@
       <c r="B25" s="158"/>
       <c r="C25" s="157"/>
       <c r="D25" s="157"/>
-      <c r="E25" s="160" t="s">
+      <c r="E25" s="159" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="160"/>
-      <c r="G25" s="160" t="s">
+      <c r="F25" s="159"/>
+      <c r="G25" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="160"/>
+      <c r="H25" s="159"/>
       <c r="I25" s="157"/>
       <c r="J25" s="157"/>
       <c r="K25" s="157"/>
-      <c r="L25" s="160" t="s">
+      <c r="L25" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="M25" s="160"/>
-      <c r="N25" s="160"/>
-      <c r="O25" s="160" t="s">
+      <c r="M25" s="159"/>
+      <c r="N25" s="159"/>
+      <c r="O25" s="159" t="s">
         <v>42</v>
       </c>
-      <c r="P25" s="160"/>
-      <c r="Q25" s="160"/>
+      <c r="P25" s="159"/>
+      <c r="Q25" s="159"/>
       <c r="R25" s="157"/>
       <c r="S25" s="157"/>
       <c r="T25" s="157"/>
-      <c r="U25" s="160" t="s">
+      <c r="U25" s="159" t="s">
         <v>43</v>
       </c>
-      <c r="V25" s="160"/>
-      <c r="W25" s="160"/>
-      <c r="X25" s="160"/>
-      <c r="Y25" s="160"/>
-      <c r="Z25" s="160"/>
-      <c r="AA25" s="161" t="s">
+      <c r="V25" s="159"/>
+      <c r="W25" s="159"/>
+      <c r="X25" s="159"/>
+      <c r="Y25" s="159"/>
+      <c r="Z25" s="159"/>
+      <c r="AA25" s="160" t="s">
         <v>44</v>
       </c>
-      <c r="AB25" s="161"/>
-      <c r="AC25" s="161"/>
+      <c r="AB25" s="160"/>
+      <c r="AC25" s="160"/>
       <c r="AD25"/>
     </row>
     <row r="26" spans="1:47" ht="25.8" customHeight="1">
@@ -4943,17 +5165,17 @@
       <c r="B26" s="158"/>
       <c r="C26" s="157"/>
       <c r="D26" s="157"/>
-      <c r="E26" s="160"/>
-      <c r="F26" s="160"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="160"/>
+      <c r="E26" s="159"/>
+      <c r="F26" s="159"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="159"/>
       <c r="I26" s="67" t="s">
         <v>41</v>
       </c>
       <c r="J26" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="K26" s="160" t="s">
+      <c r="K26" s="159" t="s">
         <v>2</v>
       </c>
       <c r="L26" s="67" t="s">
@@ -4962,7 +5184,7 @@
       <c r="M26" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="N26" s="160" t="s">
+      <c r="N26" s="159" t="s">
         <v>2</v>
       </c>
       <c r="O26" s="67" t="s">
@@ -4971,7 +5193,7 @@
       <c r="P26" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="Q26" s="160" t="s">
+      <c r="Q26" s="159" t="s">
         <v>2</v>
       </c>
       <c r="R26" s="67" t="s">
@@ -4980,22 +5202,22 @@
       <c r="S26" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="T26" s="160" t="s">
+      <c r="T26" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="U26" s="160" t="s">
+      <c r="U26" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="V26" s="160"/>
-      <c r="W26" s="160"/>
-      <c r="X26" s="160" t="s">
+      <c r="V26" s="159"/>
+      <c r="W26" s="159"/>
+      <c r="X26" s="159" t="s">
         <v>42</v>
       </c>
-      <c r="Y26" s="160"/>
-      <c r="Z26" s="160"/>
-      <c r="AA26" s="161"/>
-      <c r="AB26" s="161"/>
-      <c r="AC26" s="161"/>
+      <c r="Y26" s="159"/>
+      <c r="Z26" s="159"/>
+      <c r="AA26" s="160"/>
+      <c r="AB26" s="160"/>
+      <c r="AC26" s="160"/>
       <c r="AD26"/>
     </row>
     <row r="27" spans="1:47" ht="25.8" customHeight="1">
@@ -5025,28 +5247,28 @@
       <c r="J27" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="K27" s="160"/>
+      <c r="K27" s="159"/>
       <c r="L27" s="67" t="s">
         <v>12</v>
       </c>
       <c r="M27" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N27" s="160"/>
+      <c r="N27" s="159"/>
       <c r="O27" s="67" t="s">
         <v>12</v>
       </c>
       <c r="P27" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="Q27" s="160"/>
+      <c r="Q27" s="159"/>
       <c r="R27" s="67" t="s">
         <v>12</v>
       </c>
       <c r="S27" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="T27" s="160"/>
+      <c r="T27" s="159"/>
       <c r="U27" s="67" t="s">
         <v>45</v>
       </c>
@@ -5075,27 +5297,27 @@
         <v>2</v>
       </c>
       <c r="AD27"/>
-      <c r="AE27" s="159" t="s">
+      <c r="AE27" s="161" t="s">
         <v>47</v>
       </c>
-      <c r="AF27" s="159"/>
-      <c r="AG27" s="159"/>
-      <c r="AH27" s="159"/>
-      <c r="AI27" s="159"/>
-      <c r="AK27" s="159" t="s">
+      <c r="AF27" s="161"/>
+      <c r="AG27" s="161"/>
+      <c r="AH27" s="161"/>
+      <c r="AI27" s="161"/>
+      <c r="AK27" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="AL27" s="159"/>
-      <c r="AM27" s="159"/>
-      <c r="AN27" s="159"/>
-      <c r="AO27" s="159"/>
-      <c r="AQ27" s="159" t="s">
+      <c r="AL27" s="161"/>
+      <c r="AM27" s="161"/>
+      <c r="AN27" s="161"/>
+      <c r="AO27" s="161"/>
+      <c r="AQ27" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="AR27" s="159"/>
-      <c r="AS27" s="159"/>
-      <c r="AT27" s="159"/>
-      <c r="AU27" s="159"/>
+      <c r="AR27" s="161"/>
+      <c r="AS27" s="161"/>
+      <c r="AT27" s="161"/>
+      <c r="AU27" s="161"/>
     </row>
     <row r="28" spans="1:47" ht="18" customHeight="1">
       <c r="A28" s="67" t="s">
@@ -5227,7 +5449,7 @@
         <v>0.3</v>
       </c>
       <c r="J29" s="77">
-        <f>ChiLenhHCKT!F8-Dan!I29</f>
+        <f>ChiLenhHCKT!F8-I29</f>
         <v>-0.3</v>
       </c>
       <c r="K29" s="78">
@@ -5258,7 +5480,7 @@
         <v>1.25</v>
       </c>
       <c r="S29" s="77">
-        <f>ChiLenhHCKT!E8-Dan!R29</f>
+        <f>ChiLenhHCKT!E8-R29</f>
         <v>-1.25</v>
       </c>
       <c r="T29" s="78">
@@ -5472,7 +5694,7 @@
         <v>0.1</v>
       </c>
       <c r="J31" s="77">
-        <f>ChiLenhHCKT!F9-Dan!I31</f>
+        <f>ChiLenhHCKT!F9-I31</f>
         <v>-0.1</v>
       </c>
       <c r="K31" s="78">
@@ -5503,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="S31" s="77">
-        <f>ChiLenhHCKT!E9-Dan!R31</f>
+        <f>ChiLenhHCKT!E9-R31</f>
         <v>-1</v>
       </c>
       <c r="T31" s="78">
@@ -5631,7 +5853,7 @@
         <v>0.1</v>
       </c>
       <c r="J32" s="77">
-        <f>ChiLenhHCKT!F10-Dan!I32</f>
+        <f>ChiLenhHCKT!F10-I32</f>
         <v>-0.1</v>
       </c>
       <c r="K32" s="78">
@@ -5662,7 +5884,7 @@
         <v>1</v>
       </c>
       <c r="S32" s="77">
-        <f>ChiLenhHCKT!E10-Dan!R32</f>
+        <f>ChiLenhHCKT!E10-R32</f>
         <v>-1</v>
       </c>
       <c r="T32" s="78">
@@ -5790,7 +6012,7 @@
         <v>0.1</v>
       </c>
       <c r="J33" s="77">
-        <f>ChiLenhHCKT!F11-Dan!I33</f>
+        <f>ChiLenhHCKT!F11-I33</f>
         <v>-0.1</v>
       </c>
       <c r="K33" s="78">
@@ -5821,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="77">
-        <f>ChiLenhHCKT!E11-Dan!R33</f>
+        <f>ChiLenhHCKT!E11-R33</f>
         <v>-1</v>
       </c>
       <c r="T33" s="78">
@@ -5949,7 +6171,7 @@
         <v>0.2</v>
       </c>
       <c r="J34" s="77">
-        <f>ChiLenhHCKT!F12-Dan!I34</f>
+        <f>ChiLenhHCKT!F12-I34</f>
         <v>-0.2</v>
       </c>
       <c r="K34" s="78">
@@ -5980,7 +6202,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="77">
-        <f>ChiLenhHCKT!E12-Dan!R34</f>
+        <f>ChiLenhHCKT!E12-R34</f>
         <v>-1</v>
       </c>
       <c r="T34" s="78">
@@ -6194,7 +6416,7 @@
         <v>0.33</v>
       </c>
       <c r="J36" s="84">
-        <f>ChiLenhHCKT!F13-Dan!I36</f>
+        <f>ChiLenhHCKT!F13-I36</f>
         <v>-0.33</v>
       </c>
       <c r="K36" s="78">
@@ -6225,7 +6447,7 @@
         <v>1.25</v>
       </c>
       <c r="S36" s="84">
-        <f>ChiLenhHCKT!E13-Dan!R36</f>
+        <f>ChiLenhHCKT!E13-R36</f>
         <v>-1.25</v>
       </c>
       <c r="T36" s="78">
@@ -6353,7 +6575,7 @@
         <v>0.5</v>
       </c>
       <c r="J37" s="84">
-        <f>ChiLenhHCKT!F7-Dan!I37</f>
+        <f>ChiLenhHCKT!F7-I37</f>
         <v>-0.5</v>
       </c>
       <c r="K37" s="78">
@@ -6384,7 +6606,7 @@
         <v>1.25</v>
       </c>
       <c r="S37" s="84">
-        <f>ChiLenhHCKT!E7-Dan!R37</f>
+        <f>ChiLenhHCKT!E7-R37</f>
         <v>-1.25</v>
       </c>
       <c r="T37" s="78">
@@ -6512,7 +6734,7 @@
         <v>0.5</v>
       </c>
       <c r="J38" s="77">
-        <f>ChiLenhHCKT!F6-Dan!I38</f>
+        <f>ChiLenhHCKT!F6-I38</f>
         <v>-0.5</v>
       </c>
       <c r="K38" s="78">
@@ -6543,7 +6765,7 @@
         <v>1.25</v>
       </c>
       <c r="S38" s="77">
-        <f>ChiLenhHCKT!E6-Dan!R38</f>
+        <f>ChiLenhHCKT!E6-R38</f>
         <v>-1.25</v>
       </c>
       <c r="T38" s="78">
@@ -6671,7 +6893,7 @@
         <v>0.5</v>
       </c>
       <c r="J39" s="77">
-        <f>ChiLenhHCKT!F6-Dan!I39</f>
+        <f>ChiLenhHCKT!F6-I39</f>
         <v>-0.5</v>
       </c>
       <c r="K39" s="78">
@@ -6702,7 +6924,7 @@
         <v>1.25</v>
       </c>
       <c r="S39" s="77">
-        <f>ChiLenhHCKT!E6-Dan!R39</f>
+        <f>ChiLenhHCKT!E6-R39</f>
         <v>-1.25</v>
       </c>
       <c r="T39" s="78">
@@ -6830,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="77">
-        <f>ChiLenhHCKT!F5-Dan!I40</f>
+        <f>ChiLenhHCKT!F5-I40</f>
         <v>-1</v>
       </c>
       <c r="K40" s="78">
@@ -6861,7 +7083,7 @@
         <v>1.25</v>
       </c>
       <c r="S40" s="77">
-        <f>ChiLenhHCKT!E5-Dan!R40</f>
+        <f>ChiLenhHCKT!E5-R40</f>
         <v>-1.25</v>
       </c>
       <c r="T40" s="78">
@@ -6989,7 +7211,7 @@
         <v>2403</v>
       </c>
       <c r="J41" s="77">
-        <f>ChiLenhHCKT!F14-Dan!I41</f>
+        <f>ChiLenhHCKT!F14-I41</f>
         <v>-2403</v>
       </c>
       <c r="K41" s="69">
@@ -7020,7 +7242,7 @@
         <v>2403</v>
       </c>
       <c r="S41" s="77">
-        <f>ChiLenhHCKT!E14-Dan!R41</f>
+        <f>ChiLenhHCKT!E14-R41</f>
         <v>-2403</v>
       </c>
       <c r="T41" s="69">
@@ -7142,13 +7364,13 @@
       <c r="AB42" s="95"/>
       <c r="AC42" s="95"/>
       <c r="AD42"/>
-      <c r="AE42" s="159" t="s">
+      <c r="AE42" s="161" t="s">
         <v>72</v>
       </c>
-      <c r="AF42" s="159"/>
-      <c r="AG42" s="159"/>
-      <c r="AH42" s="159"/>
-      <c r="AI42" s="159"/>
+      <c r="AF42" s="161"/>
+      <c r="AG42" s="161"/>
+      <c r="AH42" s="161"/>
+      <c r="AI42" s="161"/>
       <c r="AJ42" s="87"/>
     </row>
     <row r="43" spans="1:47" ht="18.600000000000001" customHeight="1">
@@ -8723,13 +8945,13 @@
       <c r="AA57" s="95"/>
       <c r="AB57" s="95"/>
       <c r="AC57" s="95"/>
-      <c r="AE57" s="159" t="s">
+      <c r="AE57" s="161" t="s">
         <v>75</v>
       </c>
-      <c r="AF57" s="159"/>
-      <c r="AG57" s="159"/>
-      <c r="AH57" s="159"/>
-      <c r="AI57" s="159"/>
+      <c r="AF57" s="161"/>
+      <c r="AG57" s="161"/>
+      <c r="AH57" s="161"/>
+      <c r="AI57" s="161"/>
     </row>
     <row r="58" spans="1:36" ht="18">
       <c r="A58" s="114" t="s">
@@ -10278,13 +10500,13 @@
       <c r="AA72" s="95"/>
       <c r="AB72" s="95"/>
       <c r="AC72" s="95"/>
-      <c r="AE72" s="159" t="s">
+      <c r="AE72" s="161" t="s">
         <v>77</v>
       </c>
-      <c r="AF72" s="159"/>
-      <c r="AG72" s="159"/>
-      <c r="AH72" s="159"/>
-      <c r="AI72" s="159"/>
+      <c r="AF72" s="161"/>
+      <c r="AG72" s="161"/>
+      <c r="AH72" s="161"/>
+      <c r="AI72" s="161"/>
     </row>
     <row r="73" spans="1:35" ht="18">
       <c r="A73" s="127" t="s">
@@ -11830,13 +12052,13 @@
       <c r="AA87" s="95"/>
       <c r="AB87" s="95"/>
       <c r="AC87" s="95"/>
-      <c r="AE87" s="159" t="s">
+      <c r="AE87" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="AF87" s="159"/>
-      <c r="AG87" s="159"/>
-      <c r="AH87" s="159"/>
-      <c r="AI87" s="159"/>
+      <c r="AF87" s="161"/>
+      <c r="AG87" s="161"/>
+      <c r="AH87" s="161"/>
+      <c r="AI87" s="161"/>
     </row>
     <row r="88" spans="1:35" ht="18">
       <c r="A88" s="139" t="s">
